--- a/Configs/GameConfig/Datas/LevelConfig.xlsx
+++ b/Configs/GameConfig/Datas/LevelConfig.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -449,7 +449,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>BgmPath</t>
+          <t>BgmSoundId</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>Sound.SoundId</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>背景音乐路径(待迁)</t>
+          <t>关卡背景音乐(SoundConfig;None=无;触发者在此,按 Configs/AGENTS.md 音效定稿)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -593,7 +593,11 @@
           <t>res://TheGame/Scenes/Level_1.tscn</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Level1Bgm</t>
+        </is>
+      </c>
       <c r="H6" t="n">
         <v>6</v>
       </c>

--- a/Configs/GameConfig/Datas/LevelConfig.xlsx
+++ b/Configs/GameConfig/Datas/LevelConfig.xlsx
@@ -7,9 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LevelConfig" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LevelConfig'!$B$4:$S$9</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +27,40 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <color rgb="00425466"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00274B69"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E5EEF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F7FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +75,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,439 +454,551 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>RowId</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>LevelId</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>LegacyId</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>NameCn</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Desc</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>ScenePath</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>PlayerSpawnPointId</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>StageCount</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>*Stages</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+      <c r="S1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>StageOrder</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>StageName</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>Activation</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>TriggerId</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ClearPolicy</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>GateId</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>MaxActive</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>IsFinal</t>
-        </is>
-      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>SpawnDelay</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>*Recipes</t>
+        </is>
+      </c>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
+      <c r="S2" s="1" t="n"/>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="n"/>
+      <c r="I3" s="1" t="n"/>
+      <c r="J3" s="1" t="n"/>
+      <c r="K3" s="1" t="n"/>
+      <c r="L3" s="1" t="n"/>
+      <c r="M3" s="1" t="n"/>
+      <c r="N3" s="1" t="n"/>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>MonsterEntityId</t>
+        </is>
+      </c>
+      <c r="P3" s="1" t="inlineStr">
+        <is>
+          <t>SpawnPointId</t>
+        </is>
+      </c>
+      <c r="Q3" s="1" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="R3" s="1" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>Interval</t>
+        </is>
+      </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>##type</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Level.StageActivation</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Level.StageClearPolicy</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>bool</t>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>关卡 ID（主键）</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>旧关卡编号</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>关卡名称</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>关卡说明</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>场景资源路径</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>玩家出生点 ID</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>阶段顺序（*Stages：每行一个阶段）</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>阶段名称</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>激活方式</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>特殊触发区 ID（可空）</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>右界门 ID（末段可空）</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>最大并存数量</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>阶段生成延迟（秒）</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>怪物枚举（*Recipes：同阶段并行）</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>生成点 ID</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>生成数量</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>配方追加延迟（秒）</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>生成间隔（秒）</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>##group</t>
-        </is>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="3" t="n"/>
+      <c r="B5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>花果山·水帘洞</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>首个可运行关卡</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>res://TheGame/Scenes/Level_1.tscn</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>player_start</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>入口战</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>CameraArrived</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>stage_1_gate</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>HuaguoshanMonkey</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>stage_1_a</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>0.4</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>##</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>稳定行ID（不是关卡查询键）</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>关卡ID（分组键，每个阶段行重复）</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>旧项目关卡编号（仅首行填写）</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>关卡名（仅首行填写）</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>关卡说明（仅首行填写）</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>场景资源路径（仅首行填写）</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>玩家出生点ID（仅首行填写）</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>阶段数量（仅首行填写）</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>阶段顺序</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>阶段名</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>激活方式</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>触发器ID</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>清除规则</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>最大并存数</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>是否最终阶段</t>
-        </is>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>HuaguoshanMonkey</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>stage_1_b</t>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="4" t="n">
+        <v>0.4</v>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" t="n">
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="3" t="n"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>林间战</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>CameraArrived</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="n"/>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>stage_2_gate</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>HuaguoshanMonkey</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>stage_2_a</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>山道战</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>CameraArrived</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>stage_3_gate</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>HuaguoshanMonkey</t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="inlineStr">
+        <is>
+          <t>stage_3_a</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="4" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="3" t="n"/>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>洞口战</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>CameraArrived</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="n"/>
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>HuaguoshanMonkey</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>stage_4_a</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>花果山·水帘洞</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>首个可运行关卡</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>res://TheGame/Scenes/Level_1.tscn</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>player_start</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>入口战</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>OnEnter</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>KillAll</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>6</v>
-      </c>
-      <c r="P6" t="b">
+      <c r="R9" s="3" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>林间战</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Trigger</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>stage_2_trigger</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>KillAll</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>6</v>
-      </c>
-      <c r="P7" t="b">
+      <c r="S9" s="3" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>山道战</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Trigger</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>stage_3_trigger</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>KillAll</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>6</v>
-      </c>
-      <c r="P8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="n">
-        <v>4</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>洞口战</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Trigger</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>stage_4_trigger</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>KillAll</t>
-        </is>
-      </c>
-      <c r="O9" t="n">
-        <v>6</v>
-      </c>
-      <c r="P9" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="B4:S9"/>
+  <mergeCells count="2">
+    <mergeCell ref="H1:S1"/>
+    <mergeCell ref="O2:S2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Configs/GameConfig/Datas/LevelConfig.xlsx
+++ b/Configs/GameConfig/Datas/LevelConfig.xlsx
@@ -519,17 +519,6 @@
           <t>*Stages</t>
         </is>
       </c>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="n"/>
-      <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
-      <c r="N1" s="1" t="n"/>
-      <c r="O1" s="1" t="n"/>
-      <c r="P1" s="1" t="n"/>
-      <c r="Q1" s="1" t="n"/>
-      <c r="R1" s="1" t="n"/>
-      <c r="S1" s="1" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
@@ -583,10 +572,6 @@
           <t>*Recipes</t>
         </is>
       </c>
-      <c r="P2" s="1" t="n"/>
-      <c r="Q2" s="1" t="n"/>
-      <c r="R2" s="1" t="n"/>
-      <c r="S2" s="1" t="n"/>
     </row>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
@@ -800,7 +785,7 @@
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
@@ -835,7 +820,7 @@
         <v>0</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
@@ -888,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
@@ -941,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.35</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">

--- a/Configs/GameConfig/Datas/LevelConfig.xlsx
+++ b/Configs/GameConfig/Datas/LevelConfig.xlsx
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U15"/>
+  <dimension ref="A1:Z18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1035,6 +1035,10 @@
     <col width="14" customWidth="1" min="17" max="17"/>
     <col width="24" customWidth="1" min="18" max="18"/>
     <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="21" customWidth="1" min="23" max="23"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="21" customWidth="1" min="25" max="25"/>
+    <col width="24" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1132,6 +1136,11 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>FeaturedOpponentId</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>*Recipes</t>
         </is>
       </c>
@@ -1142,29 +1151,49 @@
           <t>##var</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MonsterEntityId</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>SpawnPointId</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Delay</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Interval</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>HealthMultiplier</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>DefenseMultiplier</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>AttackMultiplier</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>ExperienceOverride</t>
         </is>
       </c>
     </row>
@@ -1251,27 +1280,52 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>怪物枚举（同阶段并行）</t>
+          <t>守关展示怪物枚举；不改变实体继承或战斗逻辑</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
+          <t>怪物枚举；基础配置一一对应，差异使用本配方倍率</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
           <t>生成点 ID</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>生成数量</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>首只等待秒（原版 delay + interval）</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>后续间隔秒</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>生命倍率；1 为基础值，必须为有限正数</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>物理防御倍率；1 为基础值，有限且非负；不影响魔防</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>全部招式威力倍率；1 为基础值，有限且非负</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>击败经验覆盖；-1 使用基础奖励，0 不给经验</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1343,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>已接入官方前四波位置、时序与重叠区域；第五波大猩猩 Boss 尚未实现</t>
+          <t>官方五波编排；清场后靠近出口按 W 通关保存</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1333,22 +1387,39 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>HuaguoshanMonkey</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>stage_1_a</t>
         </is>
-      </c>
-      <c r="S5" t="n">
-        <v>3</v>
       </c>
       <c r="T5" t="n">
         <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
@@ -1383,64 +1454,105 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>HuaguoshanMonkey</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>stage_2_a</t>
         </is>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>5</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>3</v>
       </c>
-      <c r="U6" t="n">
-        <v>1</v>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>DemonMonkey</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>stage_2_b</t>
         </is>
       </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
       <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
         <v>6</v>
       </c>
-      <c r="U7" t="n">
-        <v>1</v>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>DemonMonkey</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>stage_2_c</t>
         </is>
       </c>
-      <c r="S8" t="n">
-        <v>1</v>
-      </c>
       <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
         <v>6</v>
       </c>
-      <c r="U8" t="n">
-        <v>1</v>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
@@ -1475,85 +1587,138 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
           <t>DemonMonkey</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>stage_3_a</t>
         </is>
       </c>
-      <c r="S9" t="n">
-        <v>1</v>
-      </c>
       <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
         <v>4</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>2</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>DemonMonkey</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>stage_3_b</t>
         </is>
       </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
       <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
         <v>4</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>2</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>DemonMonkey</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>stage_3_c</t>
         </is>
       </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
       <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
         <v>4</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>2</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>DemonMonkey</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>stage_3_d</t>
         </is>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>3</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>6</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>2</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="13">
@@ -1588,70 +1753,244 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
           <t>HuaguoshanMonkey</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>stage_4_a</t>
         </is>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>5</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>3</v>
       </c>
-      <c r="U13" t="n">
-        <v>1</v>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="14">
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>DemonMonkey</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>stage_4_b</t>
         </is>
       </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
       <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
         <v>4</v>
       </c>
-      <c r="U14" t="n">
-        <v>1</v>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="15">
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>DemonMonkey</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>stage_4_c</t>
         </is>
       </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
       <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
         <v>6</v>
       </c>
-      <c r="U15" t="n">
-        <v>1</v>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="I16" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>守关战</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>CameraArrived</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>stage_5_left</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>stage_5_gate</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>6</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Gorilla</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Gorilla</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>stage_5_a</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>DemonMonkey</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>stage_5_b</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>DemonMonkey</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>stage_5_c</t>
+        </is>
+      </c>
+      <c r="T18" t="n">
+        <v>5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>9</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="Q2:U2"/>
-    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="R2:Z2"/>
+    <mergeCell ref="I1:Z1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/LevelConfig.xlsx
+++ b/Configs/GameConfig/Datas/LevelConfig.xlsx
@@ -1,172 +1,173 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LevelConfig" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LevelConfig" sheetId="1" r:id="Rc6afefb245764d19"/>
   </sheets>
-  <definedNames/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="23">
     <font>
-      <name val="宋体"/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <b val="1"/>
       <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
       <color rgb="FF425466"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u val="single"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
       <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u val="single"/>
       <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
       <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
       <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <b val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <b val="1"/>
       <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <b val="1"/>
-      <color theme="3"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
       <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <b val="1"/>
       <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <b val="1"/>
       <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <b val="1"/>
       <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
       <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <b val="1"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
       <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
       <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
       <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
       <color theme="0"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="宋体"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="37">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -602,17 +603,17 @@
     </xf>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1009,324 +1010,325 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Z18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="37.95454406738281" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="24" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
-    <col width="21" customWidth="1" min="23" max="23"/>
-    <col width="21" customWidth="1" min="24" max="24"/>
-    <col width="21" customWidth="1" min="25" max="25"/>
-    <col width="24" customWidth="1" min="26" max="26"/>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="37.95454406738281" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="11" max="12" width="24" customWidth="1"/>
+    <col min="13" max="13" width="16" customWidth="1"/>
+    <col min="14" max="14" width="22" customWidth="1"/>
+    <col min="15" max="15" width="30" customWidth="1"/>
+    <col min="16" max="16" width="24" customWidth="1"/>
+    <col min="17" max="17" width="14" customWidth="1"/>
+    <col min="18" max="18" width="24" customWidth="1"/>
+    <col min="19" max="19" width="18" customWidth="1"/>
+    <col min="23" max="23" width="21" customWidth="1"/>
+    <col min="24" max="24" width="21" customWidth="1"/>
+    <col min="25" max="25" width="21" customWidth="1"/>
+    <col min="26" max="26" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>##var</t>
+          <t xml:space="preserve">##var</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>LevelId</t>
+          <t xml:space="preserve">LevelId</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>LegacyId</t>
+          <t xml:space="preserve">LegacyId</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>NameCn</t>
+          <t xml:space="preserve">NameCn</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Desc</t>
+          <t xml:space="preserve">Desc</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>ScenePath</t>
+          <t xml:space="preserve">ScenePath</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>MusicId</t>
+          <t xml:space="preserve">MusicId</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>PlayerSpawnPointId</t>
+          <t xml:space="preserve">PlayerSpawnPointId</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>*Stages</t>
+          <t xml:space="preserve">*Stages</t>
         </is>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>##var</t>
+          <t xml:space="preserve">##var</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>StageOrder</t>
+          <t xml:space="preserve">StageOrder</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>StageName</t>
+          <t xml:space="preserve">StageName</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Activation</t>
+          <t xml:space="preserve">Activation</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>TriggerId</t>
+          <t xml:space="preserve">TriggerId</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>LeftGateId</t>
+          <t xml:space="preserve">LeftGateId</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>GateId</t>
+          <t xml:space="preserve">GateId</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>MaxActive</t>
+          <t xml:space="preserve">MaxActive</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>SpawnDelay</t>
+          <t xml:space="preserve">SpawnDelay</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>FeaturedOpponentId</t>
+          <t xml:space="preserve">FeaturedOpponentId</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>*Recipes</t>
+          <t xml:space="preserve">*Recipes</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>##var</t>
+          <t xml:space="preserve">##var</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>MonsterEntityId</t>
+          <t xml:space="preserve">MonsterEntityId</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>SpawnPointId</t>
+          <t xml:space="preserve">SpawnPointId</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Count</t>
+          <t xml:space="preserve">Count</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Delay</t>
+          <t xml:space="preserve">Delay</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Interval</t>
+          <t xml:space="preserve">Interval</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>HealthMultiplier</t>
+          <t xml:space="preserve">HealthMultiplier</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>DefenseMultiplier</t>
+          <t xml:space="preserve">DefenseMultiplier</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>AttackMultiplier</t>
+          <t xml:space="preserve">AttackMultiplier</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>ExperienceOverride</t>
-        </is>
+          <t xml:space="preserve">ExperienceOverride</t>
+        </is>
+      </c>
+      <c r="AA3" t="str">
+        <v>EquipmentDropPoolOverride</v>
       </c>
     </row>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>##</t>
+          <t xml:space="preserve">##</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>关卡 ID（主键）</t>
+          <t xml:space="preserve">关卡 ID（主键）</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>旧关卡编号</t>
+          <t xml:space="preserve">旧关卡编号</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>关卡名称</t>
+          <t xml:space="preserve">关卡名称</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>关卡说明</t>
+          <t xml:space="preserve">关卡说明</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>场景资源路径</t>
+          <t xml:space="preserve">场景资源路径</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>本关背景音乐枚举</t>
+          <t xml:space="preserve">本关背景音乐枚举</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>玩家出生点 ID</t>
+          <t xml:space="preserve">玩家出生点 ID</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>阶段顺序</t>
+          <t xml:space="preserve">阶段顺序</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>阶段名称</t>
+          <t xml:space="preserve">阶段名称</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>激活方式</t>
+          <t xml:space="preserve">激活方式</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>特殊触发区 ID（可空）</t>
+          <t xml:space="preserve">特殊触发区 ID（可空）</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>左界门 ID（空为场景左墙）</t>
+          <t xml:space="preserve">左界门 ID（空为场景左墙）</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>右界门 ID（空为场景右墙）</t>
+          <t xml:space="preserve">右界门 ID（空为场景右墙）</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>最大并存数量</t>
+          <t xml:space="preserve">最大并存数量</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>阶段生成延迟（秒）</t>
+          <t xml:space="preserve">阶段生成延迟（秒）</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>守关展示怪物枚举；不改变实体继承或战斗逻辑</t>
+          <t xml:space="preserve">守关展示怪物枚举；不改变实体继承或战斗逻辑</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>怪物枚举；基础配置一一对应，差异使用本配方倍率</t>
+          <t xml:space="preserve">怪物枚举；基础配置一一对应，差异使用本配方倍率</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>生成点 ID</t>
+          <t xml:space="preserve">生成点 ID</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>生成数量</t>
+          <t xml:space="preserve">生成数量</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>首只等待秒（原版 delay + interval）</t>
+          <t xml:space="preserve">首只等待秒（原版 delay + interval）</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>后续间隔秒</t>
+          <t xml:space="preserve">后续间隔秒</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>生命倍率；1 为基础值，必须为有限正数</t>
+          <t xml:space="preserve">生命倍率；1 为基础值，必须为有限正数</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>物理防御倍率；1 为基础值，有限且非负；不影响魔防</t>
+          <t xml:space="preserve">物理防御倍率；1 为基础值，有限且非负；不影响魔防</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>全部招式威力倍率；1 为基础值，有限且非负</t>
+          <t xml:space="preserve">全部招式威力倍率；1 为基础值，有限且非负</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>击败经验覆盖；-1 使用基础奖励，0 不给经验</t>
-        </is>
+          <t xml:space="preserve">击败经验覆盖；-1 使用基础奖励，0 不给经验</t>
+        </is>
+      </c>
+      <c r="AA4" t="str">
+        <v>UseMonster 使用怪物池；None 禁止掉装备（官方花果山守关猩猩）</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
@@ -1338,27 +1340,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>花果山</t>
+          <t xml:space="preserve">花果山</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>官方五波编排；清场后靠近出口按 W 通关保存</t>
+          <t xml:space="preserve">官方五波编排；清场后靠近出口按 W 通关保存</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>res://TheGame/Scenes/Level_1.tscn</t>
+          <t xml:space="preserve">res://TheGame/Scenes/Level_1.tscn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>HuaguoshanTheme</t>
+          <t xml:space="preserve">HuaguoshanTheme</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>player_start</t>
+          <t xml:space="preserve">player_start</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -1366,17 +1368,17 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>入口战</t>
+          <t xml:space="preserve">入口战</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>CameraArrived</t>
+          <t xml:space="preserve">CameraArrived</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>stage_1_gate</t>
+          <t xml:space="preserve">stage_1_gate</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -1387,17 +1389,17 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>HuaguoshanMonkey</t>
+          <t xml:space="preserve">HuaguoshanMonkey</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>stage_1_a</t>
+          <t xml:space="preserve">stage_1_a</t>
         </is>
       </c>
       <c r="T5" t="n">
@@ -1420,6 +1422,9 @@
       </c>
       <c r="Z5" t="n">
         <v>-1</v>
+      </c>
+      <c r="AA5" t="str">
+        <v>继承怪物</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
@@ -1428,22 +1433,22 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>林间战</t>
+          <t xml:space="preserve">林间战</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>CameraArrived</t>
+          <t xml:space="preserve">CameraArrived</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>stage_2_left</t>
+          <t xml:space="preserve">stage_2_left</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>stage_2_gate</t>
+          <t xml:space="preserve">stage_2_gate</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -1454,17 +1459,17 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>HuaguoshanMonkey</t>
+          <t xml:space="preserve">HuaguoshanMonkey</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>stage_2_a</t>
+          <t xml:space="preserve">stage_2_a</t>
         </is>
       </c>
       <c r="T6" t="n">
@@ -1487,17 +1492,20 @@
       </c>
       <c r="Z6" t="n">
         <v>-1</v>
+      </c>
+      <c r="AA6" t="str">
+        <v>继承怪物</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="R7" t="inlineStr">
         <is>
-          <t>DemonMonkey</t>
+          <t xml:space="preserve">DemonMonkey</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>stage_2_b</t>
+          <t xml:space="preserve">stage_2_b</t>
         </is>
       </c>
       <c r="T7" t="n">
@@ -1520,17 +1528,20 @@
       </c>
       <c r="Z7" t="n">
         <v>-1</v>
+      </c>
+      <c r="AA7" t="str">
+        <v>继承怪物</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="R8" t="inlineStr">
         <is>
-          <t>DemonMonkey</t>
+          <t xml:space="preserve">DemonMonkey</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>stage_2_c</t>
+          <t xml:space="preserve">stage_2_c</t>
         </is>
       </c>
       <c r="T8" t="n">
@@ -1553,6 +1564,9 @@
       </c>
       <c r="Z8" t="n">
         <v>-1</v>
+      </c>
+      <c r="AA8" t="str">
+        <v>继承怪物</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
@@ -1561,22 +1575,22 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>山道战</t>
+          <t xml:space="preserve">山道战</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>CameraArrived</t>
+          <t xml:space="preserve">CameraArrived</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>stage_3_left</t>
+          <t xml:space="preserve">stage_3_left</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>stage_3_gate</t>
+          <t xml:space="preserve">stage_3_gate</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -1587,17 +1601,17 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>DemonMonkey</t>
+          <t xml:space="preserve">DemonMonkey</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>stage_3_a</t>
+          <t xml:space="preserve">stage_3_a</t>
         </is>
       </c>
       <c r="T9" t="n">
@@ -1620,17 +1634,20 @@
       </c>
       <c r="Z9" t="n">
         <v>-1</v>
+      </c>
+      <c r="AA9" t="str">
+        <v>继承怪物</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="R10" t="inlineStr">
         <is>
-          <t>DemonMonkey</t>
+          <t xml:space="preserve">DemonMonkey</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>stage_3_b</t>
+          <t xml:space="preserve">stage_3_b</t>
         </is>
       </c>
       <c r="T10" t="n">
@@ -1653,17 +1670,20 @@
       </c>
       <c r="Z10" t="n">
         <v>-1</v>
+      </c>
+      <c r="AA10" t="str">
+        <v>继承怪物</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="R11" t="inlineStr">
         <is>
-          <t>DemonMonkey</t>
+          <t xml:space="preserve">DemonMonkey</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>stage_3_c</t>
+          <t xml:space="preserve">stage_3_c</t>
         </is>
       </c>
       <c r="T11" t="n">
@@ -1686,17 +1706,20 @@
       </c>
       <c r="Z11" t="n">
         <v>-1</v>
+      </c>
+      <c r="AA11" t="str">
+        <v>继承怪物</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="R12" t="inlineStr">
         <is>
-          <t>DemonMonkey</t>
+          <t xml:space="preserve">DemonMonkey</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>stage_3_d</t>
+          <t xml:space="preserve">stage_3_d</t>
         </is>
       </c>
       <c r="T12" t="n">
@@ -1719,6 +1742,9 @@
       </c>
       <c r="Z12" t="n">
         <v>-1</v>
+      </c>
+      <c r="AA12" t="str">
+        <v>继承怪物</v>
       </c>
     </row>
     <row r="13">
@@ -1727,22 +1753,22 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>洞口战</t>
+          <t xml:space="preserve">洞口战</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>CameraArrived</t>
+          <t xml:space="preserve">CameraArrived</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>stage_4_left</t>
+          <t xml:space="preserve">stage_4_left</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>stage_4_gate</t>
+          <t xml:space="preserve">stage_4_gate</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -1753,17 +1779,17 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>HuaguoshanMonkey</t>
+          <t xml:space="preserve">HuaguoshanMonkey</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>stage_4_a</t>
+          <t xml:space="preserve">stage_4_a</t>
         </is>
       </c>
       <c r="T13" t="n">
@@ -1786,17 +1812,20 @@
       </c>
       <c r="Z13" t="n">
         <v>-1</v>
+      </c>
+      <c r="AA13" t="str">
+        <v>继承怪物</v>
       </c>
     </row>
     <row r="14">
       <c r="R14" t="inlineStr">
         <is>
-          <t>DemonMonkey</t>
+          <t xml:space="preserve">DemonMonkey</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>stage_4_b</t>
+          <t xml:space="preserve">stage_4_b</t>
         </is>
       </c>
       <c r="T14" t="n">
@@ -1819,17 +1848,20 @@
       </c>
       <c r="Z14" t="n">
         <v>-1</v>
+      </c>
+      <c r="AA14" t="str">
+        <v>继承怪物</v>
       </c>
     </row>
     <row r="15">
       <c r="R15" t="inlineStr">
         <is>
-          <t>DemonMonkey</t>
+          <t xml:space="preserve">DemonMonkey</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>stage_4_c</t>
+          <t xml:space="preserve">stage_4_c</t>
         </is>
       </c>
       <c r="T15" t="n">
@@ -1852,6 +1884,9 @@
       </c>
       <c r="Z15" t="n">
         <v>-1</v>
+      </c>
+      <c r="AA15" t="str">
+        <v>继承怪物</v>
       </c>
     </row>
     <row r="16">
@@ -1860,22 +1895,22 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>守关战</t>
+          <t xml:space="preserve">守关战</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>CameraArrived</t>
+          <t xml:space="preserve">CameraArrived</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>stage_5_left</t>
+          <t xml:space="preserve">stage_5_left</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>stage_5_gate</t>
+          <t xml:space="preserve">stage_5_gate</t>
         </is>
       </c>
       <c r="O16" t="n">
@@ -1886,17 +1921,17 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Gorilla</t>
+          <t xml:space="preserve">Gorilla</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Gorilla</t>
+          <t xml:space="preserve">Gorilla</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>stage_5_a</t>
+          <t xml:space="preserve">stage_5_a</t>
         </is>
       </c>
       <c r="T16" t="n">
@@ -1919,17 +1954,20 @@
       </c>
       <c r="Z16" t="n">
         <v>25</v>
+      </c>
+      <c r="AA16" t="str">
+        <v>不掉落</v>
       </c>
     </row>
     <row r="17">
       <c r="R17" t="inlineStr">
         <is>
-          <t>DemonMonkey</t>
+          <t xml:space="preserve">DemonMonkey</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>stage_5_b</t>
+          <t xml:space="preserve">stage_5_b</t>
         </is>
       </c>
       <c r="T17" t="n">
@@ -1952,17 +1990,20 @@
       </c>
       <c r="Z17" t="n">
         <v>-1</v>
+      </c>
+      <c r="AA17" t="str">
+        <v>继承怪物</v>
       </c>
     </row>
     <row r="18">
       <c r="R18" t="inlineStr">
         <is>
-          <t>DemonMonkey</t>
+          <t xml:space="preserve">DemonMonkey</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>stage_5_c</t>
+          <t xml:space="preserve">stage_5_c</t>
         </is>
       </c>
       <c r="T18" t="n">
@@ -1986,11 +2027,14 @@
       <c r="Z18" t="n">
         <v>-1</v>
       </c>
+      <c r="AA18" t="str">
+        <v>继承怪物</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="R2:Z2"/>
-    <mergeCell ref="I1:Z1"/>
+  <mergeCells>
+    <mergeCell ref="I1:AA1"/>
+    <mergeCell ref="R2:AA2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/LevelConfig.xlsx
+++ b/Configs/GameConfig/Datas/LevelConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LevelConfig" sheetId="1" r:id="R0c60dc3f385a446d"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LevelConfig" sheetId="1" r:id="R20c6db0db5504615"/>
   </sheets>
 </workbook>
 </file>
@@ -249,7 +249,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:X18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -495,7 +494,7 @@
         <v>官方五波编排；清场后靠近出口按 W 通关保存</v>
       </c>
       <c r="F5" s="1" t="str">
-        <v>res://TheGame/Scenes/level_1.tscn</v>
+        <v>res://TheGame/Scenes/Levels/zm1_01_huaguoshan/level_1.tscn</v>
       </c>
       <c r="G5" s="1" t="str">
         <v>player_start</v>
@@ -1176,8 +1175,1620 @@
         <v>-1</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="1" t="str">
+        <v>水帘洞</v>
+      </c>
+      <c r="E19" s="1" t="str">
+        <v>造一原版五波出生点、间隔与战斗区域</v>
+      </c>
+      <c r="F19" s="1" t="str">
+        <v>res://TheGame/Scenes/Levels/zm1_02_shuiliandong/level_2.tscn</v>
+      </c>
+      <c r="G19" s="1" t="str">
+        <v>player_start</v>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="1" t="str">
+        <v>第1波</v>
+      </c>
+      <c r="J19" s="1" t="str">
+        <v>CameraArrived</v>
+      </c>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1" t="str">
+        <v>stage_1_gate</v>
+      </c>
+      <c r="N19" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="O19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="1" t="str">
+        <v>DemonMonkey</v>
+      </c>
+      <c r="Q19" s="1" t="str">
+        <v>stage_1_a</v>
+      </c>
+      <c r="R19" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="S19" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" s="1" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1" t="str">
+        <v>HuaguoshanMonkey</v>
+      </c>
+      <c r="Q20" s="1" t="str">
+        <v>stage_1_b</v>
+      </c>
+      <c r="R20" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="S20" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="T20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" s="1" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" s="1" t="str">
+        <v>第2波</v>
+      </c>
+      <c r="J21" s="1" t="str">
+        <v>CameraArrived</v>
+      </c>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1" t="str">
+        <v>stage_2_left</v>
+      </c>
+      <c r="M21" s="1" t="str">
+        <v>stage_2_gate</v>
+      </c>
+      <c r="N21" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="O21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="1" t="str">
+        <v>DemonMonkey</v>
+      </c>
+      <c r="Q21" s="1" t="str">
+        <v>stage_2_a</v>
+      </c>
+      <c r="R21" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="S21" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="T21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X21" s="1" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1" t="str">
+        <v>HuaguoshanMonkey</v>
+      </c>
+      <c r="Q22" s="1" t="str">
+        <v>stage_2_b</v>
+      </c>
+      <c r="R22" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="S22" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X22" s="1" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1" t="str">
+        <v>DemonMonkey</v>
+      </c>
+      <c r="Q23" s="1" t="str">
+        <v>stage_2_c</v>
+      </c>
+      <c r="R23" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="S23" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="T23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X23" s="1" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1" t="str">
+        <v>DemonMonkey</v>
+      </c>
+      <c r="Q24" s="1" t="str">
+        <v>stage_2_d</v>
+      </c>
+      <c r="R24" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="S24" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X24" s="1" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1" t="str">
+        <v>DemonMonkey</v>
+      </c>
+      <c r="Q25" s="1" t="str">
+        <v>stage_2_e</v>
+      </c>
+      <c r="R25" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="S25" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X25" s="1" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" s="1" t="str">
+        <v>第3波</v>
+      </c>
+      <c r="J26" s="1" t="str">
+        <v>CameraArrived</v>
+      </c>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1" t="str">
+        <v>stage_3_left</v>
+      </c>
+      <c r="M26" s="1" t="str">
+        <v>stage_3_gate</v>
+      </c>
+      <c r="N26" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="O26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="1" t="str">
+        <v>DemonMonkey</v>
+      </c>
+      <c r="Q26" s="1" t="str">
+        <v>stage_3_a</v>
+      </c>
+      <c r="R26" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="T26" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" s="1" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1" t="str">
+        <v>DemonMonkey</v>
+      </c>
+      <c r="Q27" s="1" t="str">
+        <v>stage_3_b</v>
+      </c>
+      <c r="R27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="T27" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X27" s="1" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1" t="str">
+        <v>Gorilla</v>
+      </c>
+      <c r="Q28" s="1" t="str">
+        <v>stage_3_c</v>
+      </c>
+      <c r="R28" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="S28" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="T28" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X28" s="1" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1" t="str">
+        <v>DemonMonkey</v>
+      </c>
+      <c r="Q29" s="1" t="str">
+        <v>stage_3_d</v>
+      </c>
+      <c r="R29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S29" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="T29" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X29" s="1" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1" t="str">
+        <v>Gorilla</v>
+      </c>
+      <c r="Q30" s="1" t="str">
+        <v>stage_3_e</v>
+      </c>
+      <c r="R30" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="S30" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="T30" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X30" s="1" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I31" s="1" t="str">
+        <v>第4波</v>
+      </c>
+      <c r="J31" s="1" t="str">
+        <v>CameraArrived</v>
+      </c>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1" t="str">
+        <v>stage_4_left</v>
+      </c>
+      <c r="M31" s="1" t="str">
+        <v>stage_4_gate</v>
+      </c>
+      <c r="N31" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="O31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="1" t="str">
+        <v>DemonMonkey</v>
+      </c>
+      <c r="Q31" s="1" t="str">
+        <v>stage_4_a</v>
+      </c>
+      <c r="R31" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="S31" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V31" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X31" s="1" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1" t="str">
+        <v>Gorilla</v>
+      </c>
+      <c r="Q32" s="1" t="str">
+        <v>stage_4_b</v>
+      </c>
+      <c r="R32" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="S32" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="T32" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V32" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X32" s="1" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1" t="str">
+        <v>DemonMonkey</v>
+      </c>
+      <c r="Q33" s="1" t="str">
+        <v>stage_4_c</v>
+      </c>
+      <c r="R33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S33" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="T33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X33" s="1" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1" t="str">
+        <v>DemonMonkey</v>
+      </c>
+      <c r="Q34" s="1" t="str">
+        <v>stage_4_d</v>
+      </c>
+      <c r="R34" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="S34" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V34" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X34" s="1" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="1" t="str">
+        <v>Gorilla</v>
+      </c>
+      <c r="Q35" s="1" t="str">
+        <v>stage_4_e</v>
+      </c>
+      <c r="R35" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="S35" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="T35" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X35" s="1" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I36" s="1" t="str">
+        <v>守关战</v>
+      </c>
+      <c r="J36" s="1" t="str">
+        <v>CameraArrived</v>
+      </c>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1" t="str">
+        <v>stage_5_left</v>
+      </c>
+      <c r="M36" s="1" t="str">
+        <v>stage_5_gate</v>
+      </c>
+      <c r="N36" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="O36" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="1" t="str">
+        <v>MacaqueKing</v>
+      </c>
+      <c r="Q36" s="1" t="str">
+        <v>stage_5_a</v>
+      </c>
+      <c r="R36" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S36" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="T36" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V36" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X36" s="1" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" s="1" t="str">
+        <v>桃花源</v>
+      </c>
+      <c r="E37" s="1" t="str">
+        <v>造一原版五波出生点、间隔与战斗区域</v>
+      </c>
+      <c r="F37" s="1" t="str">
+        <v>res://TheGame/Scenes/Levels/zm1_03_taohuayuan/level_3.tscn</v>
+      </c>
+      <c r="G37" s="1" t="str">
+        <v>player_start</v>
+      </c>
+      <c r="H37" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="1" t="str">
+        <v>第1波</v>
+      </c>
+      <c r="J37" s="1" t="str">
+        <v>CameraArrived</v>
+      </c>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1" t="str">
+        <v>stage_1_gate</v>
+      </c>
+      <c r="N37" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="O37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="1" t="str">
+        <v>DemonMonkey</v>
+      </c>
+      <c r="Q37" s="1" t="str">
+        <v>stage_1_a</v>
+      </c>
+      <c r="R37" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="S37" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="T37" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X37" s="1" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" s="1" t="str">
+        <v>第2波</v>
+      </c>
+      <c r="J38" s="1" t="str">
+        <v>CameraArrived</v>
+      </c>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1" t="str">
+        <v>stage_2_left</v>
+      </c>
+      <c r="M38" s="1" t="str">
+        <v>stage_2_gate</v>
+      </c>
+      <c r="N38" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="O38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="1" t="str">
+        <v>Gorilla</v>
+      </c>
+      <c r="Q38" s="1" t="str">
+        <v>stage_2_a</v>
+      </c>
+      <c r="R38" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="S38" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="T38" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X38" s="1" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="1" t="str">
+        <v>Gorilla</v>
+      </c>
+      <c r="Q39" s="1" t="str">
+        <v>stage_2_b</v>
+      </c>
+      <c r="R39" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="S39" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="T39" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V39" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X39" s="1" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="1" t="str">
+        <v>DemonMonkey</v>
+      </c>
+      <c r="Q40" s="1" t="str">
+        <v>stage_2_c</v>
+      </c>
+      <c r="R40" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="S40" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T40" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V40" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X40" s="1" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
+      <c r="P41" s="1" t="str">
+        <v>DemonMonkey</v>
+      </c>
+      <c r="Q41" s="1" t="str">
+        <v>stage_2_d</v>
+      </c>
+      <c r="R41" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="S41" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="T41" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V41" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X41" s="1" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I42" s="1" t="str">
+        <v>第3波</v>
+      </c>
+      <c r="J42" s="1" t="str">
+        <v>CameraArrived</v>
+      </c>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1" t="str">
+        <v>stage_3_left</v>
+      </c>
+      <c r="M42" s="1" t="str">
+        <v>stage_3_gate</v>
+      </c>
+      <c r="N42" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="O42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="1" t="str">
+        <v>Gorilla</v>
+      </c>
+      <c r="Q42" s="1" t="str">
+        <v>stage_3_a</v>
+      </c>
+      <c r="R42" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="S42" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="T42" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V42" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W42" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X42" s="1" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+      <c r="O43" s="1"/>
+      <c r="P43" s="1" t="str">
+        <v>Gorilla</v>
+      </c>
+      <c r="Q43" s="1" t="str">
+        <v>stage_3_b</v>
+      </c>
+      <c r="R43" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="S43" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T43" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V43" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X43" s="1" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="O44" s="1"/>
+      <c r="P44" s="1" t="str">
+        <v>Gorilla</v>
+      </c>
+      <c r="Q44" s="1" t="str">
+        <v>stage_3_c</v>
+      </c>
+      <c r="R44" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="S44" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="T44" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V44" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X44" s="1" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I45" s="1" t="str">
+        <v>第4波</v>
+      </c>
+      <c r="J45" s="1" t="str">
+        <v>CameraArrived</v>
+      </c>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1" t="str">
+        <v>stage_4_left</v>
+      </c>
+      <c r="M45" s="1" t="str">
+        <v>stage_4_gate</v>
+      </c>
+      <c r="N45" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="O45" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="1" t="str">
+        <v>Gorilla</v>
+      </c>
+      <c r="Q45" s="1" t="str">
+        <v>stage_4_a</v>
+      </c>
+      <c r="R45" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="S45" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="T45" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V45" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X45" s="1" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
+      <c r="O46" s="1"/>
+      <c r="P46" s="1" t="str">
+        <v>Gorilla</v>
+      </c>
+      <c r="Q46" s="1" t="str">
+        <v>stage_4_b</v>
+      </c>
+      <c r="R46" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="S46" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="T46" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V46" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W46" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X46" s="1" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+      <c r="O47" s="1"/>
+      <c r="P47" s="1" t="str">
+        <v>Gorilla</v>
+      </c>
+      <c r="Q47" s="1" t="str">
+        <v>stage_4_c</v>
+      </c>
+      <c r="R47" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="S47" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="T47" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V47" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X47" s="1" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1"/>
+      <c r="O48" s="1"/>
+      <c r="P48" s="1" t="str">
+        <v>Gorilla</v>
+      </c>
+      <c r="Q48" s="1" t="str">
+        <v>stage_4_d</v>
+      </c>
+      <c r="R48" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="S48" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="T48" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V48" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W48" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X48" s="1" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I49" s="1" t="str">
+        <v>守关战</v>
+      </c>
+      <c r="J49" s="1" t="str">
+        <v>CameraArrived</v>
+      </c>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1" t="str">
+        <v>stage_5_left</v>
+      </c>
+      <c r="M49" s="1" t="str">
+        <v>stage_5_gate</v>
+      </c>
+      <c r="N49" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="O49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="1" t="str">
+        <v>TamarinKing</v>
+      </c>
+      <c r="Q49" s="1" t="str">
+        <v>stage_5_a</v>
+      </c>
+      <c r="R49" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S49" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="T49" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V49" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W49" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X49" s="1" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1"/>
+      <c r="O50" s="1"/>
+      <c r="P50" s="1" t="str">
+        <v>Gorilla</v>
+      </c>
+      <c r="Q50" s="1" t="str">
+        <v>stage_5_b</v>
+      </c>
+      <c r="R50" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="S50" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V50" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W50" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X50" s="1" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="1" t="str">
+        <v>Gorilla</v>
+      </c>
+      <c r="Q51" s="1" t="str">
+        <v>stage_5_c</v>
+      </c>
+      <c r="R51" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="S51" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="T51" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V51" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W51" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X51" s="1" t="n">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells>
     <mergeCell ref="H1:X1"/>
     <mergeCell ref="P2:X2"/>
   </mergeCells>
